--- a/artfynd/A 41337-2024 artfynd.xlsx
+++ b/artfynd/A 41337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120457670</v>
+        <v>120459711</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592448</v>
+        <v>592355</v>
       </c>
       <c r="R2" t="n">
-        <v>7037980</v>
+        <v>7037858</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120459711</v>
+        <v>120457670</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592355</v>
+        <v>592448</v>
       </c>
       <c r="R4" t="n">
-        <v>7037858</v>
+        <v>7037980</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 41337-2024 artfynd.xlsx
+++ b/artfynd/A 41337-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120459711</v>
+        <v>120457670</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592355</v>
+        <v>592448</v>
       </c>
       <c r="R2" t="n">
-        <v>7037858</v>
+        <v>7037980</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120457670</v>
+        <v>120459711</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592448</v>
+        <v>592355</v>
       </c>
       <c r="R4" t="n">
-        <v>7037980</v>
+        <v>7037858</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 41337-2024 artfynd.xlsx
+++ b/artfynd/A 41337-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120458182</v>
+        <v>120459254</v>
       </c>
       <c r="B3" t="n">
         <v>90864</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592800</v>
+        <v>592647</v>
       </c>
       <c r="R3" t="n">
-        <v>7037729</v>
+        <v>7037606</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120459254</v>
+        <v>120458182</v>
       </c>
       <c r="B5" t="n">
         <v>90864</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592647</v>
+        <v>592800</v>
       </c>
       <c r="R5" t="n">
-        <v>7037606</v>
+        <v>7037729</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
